--- a/Result/profitability/6142.xlsx
+++ b/Result/profitability/6142.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.02</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.09999999999999998</v>
+        <v>-0.08499999999999998</v>
       </c>
       <c r="N2" t="n">
-        <v>8.78375</v>
+        <v>9.91625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -783,7 +783,7 @@
         <v>-0.02124999999999998</v>
       </c>
       <c r="N3" t="n">
-        <v>9.641249999999999</v>
+        <v>10.3025</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.93</v>
       </c>
       <c r="M4" t="n">
-        <v>0.10875</v>
+        <v>0.10125</v>
       </c>
       <c r="N4" t="n">
-        <v>9.737499999999999</v>
+        <v>9.8025</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07875000000000004</v>
+        <v>0.08875000000000002</v>
       </c>
       <c r="N5" t="n">
-        <v>9.3225</v>
+        <v>9.835000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>0.12625</v>
+        <v>0.10375</v>
       </c>
       <c r="N6" t="n">
-        <v>9.495000000000001</v>
+        <v>10.05375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.28</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1525</v>
+        <v>0.15</v>
       </c>
       <c r="N7" t="n">
-        <v>9.883750000000001</v>
+        <v>11.47375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.28</v>
       </c>
       <c r="M8" t="n">
-        <v>0.19875</v>
+        <v>0.2075</v>
       </c>
       <c r="N8" t="n">
-        <v>11.2425</v>
+        <v>12.25</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6142</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>491</v>
+      </c>
+      <c r="D75" t="n">
+        <v>419</v>
+      </c>
+      <c r="E75" t="n">
+        <v>71</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-3.30%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-19</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-35</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-35</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.11125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.012499999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.06999999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3888888888888888</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.059999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.243827160493827</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4210526315789473</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3927203065134099</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
